--- a/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6071FB61-9612-424E-A746-D4AC5A73A80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{517EF2EB-B255-4539-A7BD-FF09AB0C4333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3541,7 +3541,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4504DF2B-61EB-45AC-9901-5CBEE24FAFF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{835EC839-9249-42DC-B45B-660A693DD70A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3599,7 +3599,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC8980E8-126E-4DFE-BE03-524868A5F08B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B925A3F-93FE-415F-AD43-9022E3FE551E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3657,7 +3657,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{902FA1B9-CE8E-4EE4-9808-C08A82E8D40A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BFFC988-F5A1-4546-AE1F-0974B8F47BF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3715,7 +3715,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4727ED0A-3812-4677-A52A-BB5180EDF966}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6B485B6-39A3-400D-A4CD-D44443D6E4A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3773,7 +3773,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EB2CBE9-51E6-4EDF-AC25-03BA0F3FC09E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7BF313E-7426-407A-96D8-6E7F2B213C49}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3831,7 +3831,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97723640-314C-4234-9FBC-0F32773A357F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AADBA17B-F1FD-411D-8282-C9F380D88E20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3889,7 +3889,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BD06AEB-41F5-467A-97BD-A1A259C87630}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E4F650B-C668-4721-866D-365892A67AB8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3949,7 +3949,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A5F87AA-7894-4E81-B22D-DF6496788629}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6C23D8E-EEA6-40DA-B08A-FD82AA871531}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4007,7 +4007,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A7C86BE-9828-49E4-81AD-83A9574ECAD8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A601ED9-B7B9-4958-8490-BEE681C57C2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4065,7 +4065,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E889B2A9-C65A-4264-9D98-5BA87DA9CC42}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C6D77B4-8FEB-4B46-80F1-1A75F921B852}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4125,7 +4125,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D85169C-B460-447F-A8B9-55EA60377E1B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD6AC505-A997-49ED-AAA8-A18442E347DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4181,7 +4181,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB9B1676-9EC0-4227-AF77-CAAFE7BFEE1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F23CE782-DFEF-4CFF-98FC-F246B011F9FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4239,7 +4239,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49AEDF99-EE95-485C-86AA-FD3B7961B6DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D2F2EC1-FECC-49A5-89FF-674E14790FF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4297,7 +4297,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33520549-3C35-49B3-8CD7-94E46D9BFF4E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51A8DC6B-0632-4D5D-AE18-0F136AD4F867}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4357,7 +4357,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A7A3EFC-A68C-43BB-9326-41837EA87FE4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75303DE4-4270-4CC8-91C2-0E717840D77D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4413,7 +4413,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA2A8924-AD35-4120-A2A6-C19DAB5501E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C660996F-8B42-4B7A-A394-7FF43056274B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4469,7 +4469,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFD10C6C-8C8F-4E36-A702-65A1AFB84DE2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9169FA-FEB1-44C2-B6A7-CFCEC08EAE79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4527,7 +4527,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2481282F-5ACF-443F-82BF-8B6A079DE5D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82F5A99-F743-4D7B-9713-80A13FFF61F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4585,7 +4585,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65D4FAB2-07EF-45BF-ACD1-CD9DA2204268}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9549C703-5E21-4E4B-A5F0-7BC43DBBEA3F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4647,10 +4647,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 2" descr="tmpDA88.png">
+        <xdr:cNvPr id="2" name="図 2" descr="tmp8054.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3C01088-BFBA-485C-953A-6ACDF153D0F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{906785FE-01CE-4510-AA24-41886773AAF6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4965,7 +4965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880DD2FD-D24D-437B-9DCD-75DE1E5FAEB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C5F504-827E-4930-A0C9-154724C1C4D4}">
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6024,7 +6024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3503B185-FE7F-49BF-BCD6-B88F62264516}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5733A5-C77F-4DA2-B311-40051E05878B}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7355,7 +7355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D027731-D728-4510-9DC0-55771B04C604}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6579399-52F8-4E56-B978-38ED5B7B8D58}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7492,7 +7492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190785CF-95F1-497D-93AB-963244916382}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17539C-4107-461E-ADCF-45AF6335C2E7}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>

--- a/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{517EF2EB-B255-4539-A7BD-FF09AB0C4333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00225344-E9CD-4C82-BDF5-C006EEC9AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3541,7 +3541,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{835EC839-9249-42DC-B45B-660A693DD70A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0512EE47-B138-41AE-A9D3-CCE1C6237531}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3599,7 +3599,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B925A3F-93FE-415F-AD43-9022E3FE551E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4672DBA8-02FE-4429-BF86-7B1E12476CF6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3657,7 +3657,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BFFC988-F5A1-4546-AE1F-0974B8F47BF2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7292F98A-495A-4F6D-B3E7-34191F216F88}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3715,7 +3715,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6B485B6-39A3-400D-A4CD-D44443D6E4A6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F0E9BF-D338-4EE4-8E0F-AB97F788A1A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3773,7 +3773,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7BF313E-7426-407A-96D8-6E7F2B213C49}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14299B8E-F6F5-4AE2-B54B-A31F9ED83ECF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3831,7 +3831,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AADBA17B-F1FD-411D-8282-C9F380D88E20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07A6AA6C-D727-4DFF-A52E-2CD21EA2C48A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3889,7 +3889,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E4F650B-C668-4721-866D-365892A67AB8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0231CC45-D2AD-4E65-B08F-413A4885D13C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3949,7 +3949,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6C23D8E-EEA6-40DA-B08A-FD82AA871531}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB5C694D-7443-42E5-9F3A-B8A2C6AFB7A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4007,7 +4007,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A601ED9-B7B9-4958-8490-BEE681C57C2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5487769A-F3E5-4652-915B-D999C572AC17}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4065,7 +4065,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C6D77B4-8FEB-4B46-80F1-1A75F921B852}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F465349-9B74-4518-95C8-C83F5D02C422}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4125,7 +4125,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD6AC505-A997-49ED-AAA8-A18442E347DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{047E7E4B-C16E-4612-B1E4-048CDC829ED4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4181,7 +4181,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F23CE782-DFEF-4CFF-98FC-F246B011F9FE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCDAA0ED-4F1A-4496-9528-533A189E117D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4239,7 +4239,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D2F2EC1-FECC-49A5-89FF-674E14790FF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F997D7A-7241-4A64-92EB-470830FA2296}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4297,7 +4297,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51A8DC6B-0632-4D5D-AE18-0F136AD4F867}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C21D32B4-B123-47C1-B42F-CBCA5EF637F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4357,7 +4357,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75303DE4-4270-4CC8-91C2-0E717840D77D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF62A3C2-E6DC-4C9E-A1FC-759CA311620F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4413,7 +4413,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C660996F-8B42-4B7A-A394-7FF43056274B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A906947-FF55-43FC-874E-30E8C1269A0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4469,7 +4469,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9169FA-FEB1-44C2-B6A7-CFCEC08EAE79}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54BC6214-1A7D-44F4-8E9E-C77F11679B06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4527,7 +4527,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82F5A99-F743-4D7B-9713-80A13FFF61F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{947A40CA-DADA-4E16-B6E4-1C6D1E549CF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4585,7 +4585,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9549C703-5E21-4E4B-A5F0-7BC43DBBEA3F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6437218-54F6-4343-9658-2AAC142BBC8E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4647,10 +4647,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 2" descr="tmp8054.png">
+        <xdr:cNvPr id="2" name="図 2" descr="tmpE0E5.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{906785FE-01CE-4510-AA24-41886773AAF6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D06A4167-081B-4311-B3CC-A591545B1D53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4965,7 +4965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C5F504-827E-4930-A0C9-154724C1C4D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1622E286-E298-43F0-9C17-7F55D005AEC7}">
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6024,7 +6024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5733A5-C77F-4DA2-B311-40051E05878B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A53A47-8DCB-472F-9EB2-29CB3715F1E6}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7355,7 +7355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6579399-52F8-4E56-B978-38ED5B7B8D58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70AF42F3-A74C-4D2A-95A5-74BE68B8E49E}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7492,7 +7492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17539C-4107-461E-ADCF-45AF6335C2E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6201F84-BF39-4175-9592-FC62E37340D4}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>

--- a/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00225344-E9CD-4C82-BDF5-C006EEC9AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D26A514C-241D-4DED-A83B-ED2A2F8B5F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3541,7 +3541,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0512EE47-B138-41AE-A9D3-CCE1C6237531}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50CF577-0961-4CE7-9437-6B522F97746F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3599,7 +3599,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4672DBA8-02FE-4429-BF86-7B1E12476CF6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB28BF88-4AEB-45BE-A24E-7DB7647024C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3657,7 +3657,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7292F98A-495A-4F6D-B3E7-34191F216F88}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ECC44AC-AD6C-48F1-9B19-6EADA23DDC4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3715,7 +3715,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F0E9BF-D338-4EE4-8E0F-AB97F788A1A2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{934314A9-3307-437F-8209-F8C613E54C0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3773,7 +3773,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14299B8E-F6F5-4AE2-B54B-A31F9ED83ECF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7846E9F0-8F1D-4F92-A320-31C4E7EF50C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3831,7 +3831,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07A6AA6C-D727-4DFF-A52E-2CD21EA2C48A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F9212F-812C-44B9-82F1-576996903CC8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3889,7 +3889,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0231CC45-D2AD-4E65-B08F-413A4885D13C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042ECE96-B513-41D7-8768-E06A101062D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3949,7 +3949,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB5C694D-7443-42E5-9F3A-B8A2C6AFB7A4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9F1B050-FDF7-4863-B29A-62C9B84A475C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4007,7 +4007,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5487769A-F3E5-4652-915B-D999C572AC17}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE84E9E-F979-40C8-A45A-038F98C24E2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4065,7 +4065,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F465349-9B74-4518-95C8-C83F5D02C422}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1A788BD-2A4D-4E96-8F68-A9C6CEA0DCD3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4125,7 +4125,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{047E7E4B-C16E-4612-B1E4-048CDC829ED4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD6EC37-C52E-4F3C-8A93-08C9B24332DA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4181,7 +4181,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCDAA0ED-4F1A-4496-9528-533A189E117D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B3C461D-E79C-4D01-9459-99582D65583C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4239,7 +4239,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F997D7A-7241-4A64-92EB-470830FA2296}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C6CD9CB-36AC-4380-AC85-C9522422B7AA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4297,7 +4297,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C21D32B4-B123-47C1-B42F-CBCA5EF637F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A00756F-C139-4D60-B97E-16FB092C0A52}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4357,7 +4357,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF62A3C2-E6DC-4C9E-A1FC-759CA311620F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12E75612-FDD5-4750-A900-9829477F7091}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4413,7 +4413,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A906947-FF55-43FC-874E-30E8C1269A0B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAD911C8-F70E-47B8-B0B4-0FCE07234229}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4469,7 +4469,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54BC6214-1A7D-44F4-8E9E-C77F11679B06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E441F109-7782-43A1-9EF3-971E8272992B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4527,7 +4527,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{947A40CA-DADA-4E16-B6E4-1C6D1E549CF2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BC67C1D-0C6E-4917-A825-EDF9218D8A72}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4585,7 +4585,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6437218-54F6-4343-9658-2AAC142BBC8E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9424B7B7-CC4B-485B-A33A-9D063ACD5AD7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4647,10 +4647,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 2" descr="tmpE0E5.png">
+        <xdr:cNvPr id="2" name="図 2" descr="tmpD516.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D06A4167-081B-4311-B3CC-A591545B1D53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13021DFE-C47C-4BE1-9187-CC074BC47CD1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4965,7 +4965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1622E286-E298-43F0-9C17-7F55D005AEC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0319BC-F55F-4A44-BC4C-33646AFB56CC}">
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6024,7 +6024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A53A47-8DCB-472F-9EB2-29CB3715F1E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D23FBE-4D83-4E7F-805F-8148BEEC2F54}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7355,7 +7355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70AF42F3-A74C-4D2A-95A5-74BE68B8E49E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31A7F39-4A53-4AAD-8CFE-F8FF1F9FDDA6}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7492,7 +7492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6201F84-BF39-4175-9592-FC62E37340D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AB3AE7-346F-4D98-8BD9-FDB0A9A816A0}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>

--- a/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路直角方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D26A514C-241D-4DED-A83B-ED2A2F8B5F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11C9C25-A9A6-4729-ADA2-17193DACA226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3541,7 +3541,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50CF577-0961-4CE7-9437-6B522F97746F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BC8ECC8-B3CC-4640-ABC0-C907EF2475E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3599,7 +3599,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB28BF88-4AEB-45BE-A24E-7DB7647024C3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C30644F-2801-4ADA-8FF8-F7F8AC6C15F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3657,7 +3657,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ECC44AC-AD6C-48F1-9B19-6EADA23DDC4C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1702D294-8FAF-414C-AB83-A705FCF3329B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3715,7 +3715,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{934314A9-3307-437F-8209-F8C613E54C0B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F923A3F-434A-48D8-9351-173A2826D8FF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3773,7 +3773,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7846E9F0-8F1D-4F92-A320-31C4E7EF50C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{229DAD4A-0FEC-4058-9755-95189441ECB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3831,7 +3831,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F9212F-812C-44B9-82F1-576996903CC8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A76D2C1-ACA6-459B-AB04-C98D0A5A230E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3889,7 +3889,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042ECE96-B513-41D7-8768-E06A101062D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A1D9C1D-8975-4A6F-A0D3-22505D809382}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3949,7 +3949,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9F1B050-FDF7-4863-B29A-62C9B84A475C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5929B8BD-F8F5-4368-B455-E34DC23377F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4007,7 +4007,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE84E9E-F979-40C8-A45A-038F98C24E2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{709A483D-5914-4899-AD1F-0CC7554EE52F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4065,7 +4065,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1A788BD-2A4D-4E96-8F68-A9C6CEA0DCD3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{210CBE91-E041-46D8-88EF-FCE1B25F4772}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4125,7 +4125,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD6EC37-C52E-4F3C-8A93-08C9B24332DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F18DEA-4E76-4B39-B432-EE69B15B2BA4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4181,7 +4181,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B3C461D-E79C-4D01-9459-99582D65583C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E62C2C8B-1E34-4525-ABA0-27F5753A1512}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4239,7 +4239,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C6CD9CB-36AC-4380-AC85-C9522422B7AA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3D02BA4-73E6-4845-AEDA-F40556266DFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4297,7 +4297,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A00756F-C139-4D60-B97E-16FB092C0A52}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7508934C-7A73-49A9-85F7-B4E50C2E09E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4357,7 +4357,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12E75612-FDD5-4750-A900-9829477F7091}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E578F38B-BA62-4550-B7BD-B559CA795CFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4413,7 +4413,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAD911C8-F70E-47B8-B0B4-0FCE07234229}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28CDBE2F-DBE5-481A-8535-18C2B7A40875}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4469,7 +4469,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E441F109-7782-43A1-9EF3-971E8272992B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36B0E237-2A03-4CC6-A69B-090ABB534B34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4527,7 +4527,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BC67C1D-0C6E-4917-A825-EDF9218D8A72}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B4356DF-60C9-4F1C-A767-DCE5A7E1432D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4585,7 +4585,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9424B7B7-CC4B-485B-A33A-9D063ACD5AD7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F885B608-4619-41FD-95D6-86216CEC43B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4647,10 +4647,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 2" descr="tmpD516.png">
+        <xdr:cNvPr id="2" name="図 2" descr="tmp57D6.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13021DFE-C47C-4BE1-9187-CC074BC47CD1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B68B2DE-4B2B-44B8-9C8A-76C18D50CDB3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4965,7 +4965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0319BC-F55F-4A44-BC4C-33646AFB56CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5956F57-1A0A-4A3B-912F-49EA573BC7DC}">
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6024,7 +6024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D23FBE-4D83-4E7F-805F-8148BEEC2F54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B529E8CE-23FD-4A27-A2EE-1486C800C82F}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7355,7 +7355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31A7F39-4A53-4AAD-8CFE-F8FF1F9FDDA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B32277CF-4386-4377-9090-8FC9789C4E70}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7492,7 +7492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AB3AE7-346F-4D98-8BD9-FDB0A9A816A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60B98E5-B123-47C4-B0C5-86CFA478A671}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
